--- a/assignment/Relative_Interest_Pie_Chart.xlsx
+++ b/assignment/Relative_Interest_Pie_Chart.xlsx
@@ -251,10 +251,10 @@
           <yMode val="edge"/>
           <wMode val="factor"/>
           <hMode val="factor"/>
-          <x val="0.07000000000000001"/>
-          <y val="0.2"/>
-          <w val="0.42"/>
-          <h val="0.7"/>
+          <x val="0.06"/>
+          <y val="0.17"/>
+          <w val="0.46"/>
+          <h val="0.78"/>
         </manualLayout>
       </layout>
       <pieChart>
@@ -276,13 +276,11 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="C55A11"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="bg1"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -292,13 +290,11 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="50000"/>
-                </a:schemeClr>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="bg1"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -308,13 +304,11 @@
             <idx val="2"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
+                <a:srgbClr val="0F8A5F"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="bg1"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -324,11 +318,11 @@
             <idx val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="4A3AA7"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="bg1"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -338,14 +332,11 @@
             <idx val="4"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
+                <a:srgbClr val="B03A8C"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
-                  <a:schemeClr val="bg1"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -367,9 +358,9 @@
             <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="1000" b="1">
+                <a:defRPr sz="1100" b="1">
                   <a:solidFill>
-                    <a:srgbClr val="404040"/>
+                    <a:srgbClr val="FFFFFF"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                 </a:defRPr>
@@ -377,23 +368,21 @@
               <a:r>
                 <a:t/>
               </a:r>
-              <a:endParaRPr sz="1000" b="1">
+              <a:endParaRPr sz="1100" b="1">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="FFFFFF"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:endParaRPr>
             </a:p>
           </txPr>
-          <dLblPos val="outEnd"/>
+          <dLblPos val="inEnd"/>
           <showLegendKey val="0"/>
-          <showVal val="1"/>
+          <showVal val="0"/>
           <showCatName val="0"/>
           <showSerName val="0"/>
           <showPercent val="1"/>
-          <separator>
-</separator>
-          <showLeaderLines val="1"/>
+          <showLeaderLines val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>

--- a/assignment/Relative_Interest_Pie_Chart.xlsx
+++ b/assignment/Relative_Interest_Pie_Chart.xlsx
@@ -29,7 +29,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
-      <color theme="4" tint="-0.499984740745262"/>
+      <color theme="1"/>
       <sz val="14"/>
       <scheme val="minor"/>
     </font>
@@ -75,7 +75,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.499984740745262"/>
+        <fgColor theme="1"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,10 +251,10 @@
           <yMode val="edge"/>
           <wMode val="factor"/>
           <hMode val="factor"/>
-          <x val="0.06"/>
-          <y val="0.17"/>
-          <w val="0.46"/>
-          <h val="0.78"/>
+          <x val="0.09"/>
+          <y val="0.21"/>
+          <w val="0.41"/>
+          <h val="0.7"/>
         </manualLayout>
       </layout>
       <pieChart>
@@ -276,7 +276,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="C55A11"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -290,7 +290,7 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="404040"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -304,7 +304,7 @@
             <idx val="2"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="0F8A5F"/>
+                <a:srgbClr val="7F7F7F"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -318,7 +318,7 @@
             <idx val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="4A3AA7"/>
+                <a:srgbClr val="A6A6A6"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -332,7 +332,7 @@
             <idx val="4"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="B03A8C"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -360,7 +360,7 @@
               <a:pPr>
                 <a:defRPr sz="1100" b="1">
                   <a:solidFill>
-                    <a:srgbClr val="FFFFFF"/>
+                    <a:srgbClr val="000000"/>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                 </a:defRPr>
@@ -370,19 +370,19 @@
               </a:r>
               <a:endParaRPr sz="1100" b="1">
                 <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
               </a:endParaRPr>
             </a:p>
           </txPr>
-          <dLblPos val="inEnd"/>
+          <dLblPos val="outEnd"/>
           <showLegendKey val="0"/>
           <showVal val="0"/>
           <showCatName val="0"/>
           <showSerName val="0"/>
           <showPercent val="1"/>
-          <showLeaderLines val="0"/>
+          <showLeaderLines val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>

--- a/assignment/Relative_Interest_Pie_Chart.xlsx
+++ b/assignment/Relative_Interest_Pie_Chart.xlsx
@@ -276,7 +276,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="262626"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -290,7 +290,7 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="404040"/>
+                <a:srgbClr val="A6A6A6"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -304,7 +304,7 @@
             <idx val="2"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7F7F7F"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -318,7 +318,7 @@
             <idx val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="A6A6A6"/>
+                <a:srgbClr val="D9D9D9"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
@@ -332,7 +332,7 @@
             <idx val="4"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="D9D9D9"/>
+                <a:srgbClr val="7F7F7F"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
